--- a/outputs/reports/stacked_ensemble_v2/evaluation.xlsx
+++ b/outputs/reports/stacked_ensemble_v2/evaluation.xlsx
@@ -487,37 +487,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9708487592938225</v>
+        <v>0.987136929460581</v>
       </c>
       <c r="C2" t="n">
-        <v>0.09622034100393466</v>
+        <v>0.1431623931623932</v>
       </c>
       <c r="D2" t="n">
-        <v>0.950530035335689</v>
+        <v>0.4135802469135803</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1747509744478129</v>
+        <v>0.2126984126984127</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9709149511731865</v>
+        <v>0.9895567477472785</v>
       </c>
       <c r="G2" t="n">
-        <v>253035</v>
+        <v>37997</v>
       </c>
       <c r="H2" t="n">
-        <v>7580</v>
+        <v>401</v>
       </c>
       <c r="I2" t="n">
-        <v>42</v>
+        <v>95</v>
       </c>
       <c r="J2" t="n">
-        <v>807</v>
+        <v>67</v>
       </c>
       <c r="K2" t="n">
-        <v>0.9852749658227785</v>
+        <v>0.884181612468242</v>
       </c>
       <c r="L2" t="n">
-        <v>0.8838400373657338</v>
+        <v>0.3192631950454666</v>
       </c>
     </row>
   </sheetData>
@@ -613,43 +613,43 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.003247100939326255</v>
+        <v>0.004201244813278008</v>
       </c>
       <c r="C2" t="n">
-        <v>2615</v>
+        <v>386</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3036328871892925</v>
+        <v>0.1658031088082902</v>
       </c>
       <c r="E2" t="n">
-        <v>93.50891544883531</v>
+        <v>39.46523380029425</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9352179034157833</v>
+        <v>0.3950617283950617</v>
       </c>
       <c r="G2" t="n">
-        <v>13074</v>
+        <v>1928</v>
       </c>
       <c r="H2" t="n">
-        <v>0.06195502524093621</v>
+        <v>0.0487551867219917</v>
       </c>
       <c r="I2" t="n">
-        <v>19.08010449893539</v>
+        <v>11.60493827160494</v>
       </c>
       <c r="J2" t="n">
-        <v>0.9540636042402827</v>
+        <v>0.5802469135802469</v>
       </c>
       <c r="K2" t="n">
-        <v>26147</v>
+        <v>3856</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03128465980800857</v>
+        <v>0.02930497925311203</v>
       </c>
       <c r="M2" t="n">
-        <v>9.634643453523147</v>
+        <v>6.975308641975309</v>
       </c>
       <c r="N2" t="n">
-        <v>0.9634864546525324</v>
+        <v>0.6975308641975309</v>
       </c>
     </row>
   </sheetData>
@@ -700,13 +700,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>174370</v>
+        <v>33670</v>
       </c>
       <c r="C2" t="n">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="D2" t="n">
-        <v>9.749383494867236e-05</v>
+        <v>0.001247401247401247</v>
       </c>
       <c r="E2" t="b">
         <v>0</v>
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>54111</v>
+        <v>3241</v>
       </c>
       <c r="C3" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0002587274306518083</v>
+        <v>0.008022215365627893</v>
       </c>
       <c r="E3" t="b">
         <v>0</v>
@@ -738,13 +738,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>14229</v>
+        <v>703</v>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0002811160306416474</v>
+        <v>0.0128022759601707</v>
       </c>
       <c r="E4" t="b">
         <v>0</v>
@@ -757,13 +757,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6489</v>
+        <v>307</v>
       </c>
       <c r="C5" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0006164278008938204</v>
+        <v>0.03257328990228013</v>
       </c>
       <c r="E5" t="b">
         <v>0</v>
@@ -776,13 +776,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3860</v>
+        <v>170</v>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0007772020725388601</v>
+        <v>0.04705882352941176</v>
       </c>
       <c r="E6" t="b">
         <v>0</v>
@@ -795,13 +795,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2423</v>
+        <v>138</v>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0008254230293025176</v>
+        <v>0.04347826086956522</v>
       </c>
       <c r="E7" t="b">
         <v>0</v>
@@ -814,13 +814,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1716</v>
+        <v>89</v>
       </c>
       <c r="C8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.002913752913752914</v>
+        <v>0.01123595505617977</v>
       </c>
       <c r="E8" t="b">
         <v>0</v>
@@ -833,13 +833,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1268</v>
+        <v>65</v>
       </c>
       <c r="C9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>0.003154574132492113</v>
+        <v>0.04615384615384616</v>
       </c>
       <c r="E9" t="b">
         <v>0</v>
@@ -852,13 +852,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>972</v>
+        <v>70</v>
       </c>
       <c r="C10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>0.00720164609053498</v>
+        <v>0.08571428571428572</v>
       </c>
       <c r="E10" t="b">
         <v>0</v>
@@ -871,13 +871,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2026</v>
+        <v>107</v>
       </c>
       <c r="C11" t="n">
-        <v>789</v>
+        <v>51</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3894373149062191</v>
+        <v>0.4766355140186916</v>
       </c>
       <c r="E11" t="b">
         <v>0</v>
